--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261014.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>202612ESZ6</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>202612ESZ6</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
